--- a/Periodic Table of AI.xlsx
+++ b/Periodic Table of AI.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ffpch\Desktop\CN Files\Tableau\MM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\Portfolio Projects\Project-3-Analyzing-the-Periodic-Table-of-AI-Startups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D3A9717-0303-421F-94C3-C40099FA8745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85028FB8-55E7-4F1D-9D1E-0419F4B0510D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7E968E2-4B52-42FA-943D-AAAD515C8D58}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E7E968E2-4B52-42FA-943D-AAAD515C8D58}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -268,7 +279,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,18 +340,20 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -360,9 +373,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -400,7 +413,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -506,7 +519,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -648,7 +661,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -657,544 +670,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92246C2D-7219-4231-A510-4A7087DF331D}">
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="54.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="58.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="58.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:11" ht="15" thickBot="1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:11" ht="15" thickBot="1">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>80</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>15</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>75</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:11" ht="15" thickBot="1">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>7</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>28</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>100</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="4" spans="1:11" ht="15" thickBot="1">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>13</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>48</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>260</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+    <row r="5" spans="1:11" ht="15" thickBot="1">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>8</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>42</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>150</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+    <row r="6" spans="1:11" ht="15" thickBot="1">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>4.8</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>22</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>320</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+    <row r="7" spans="1:11" ht="15" thickBot="1">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>10</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>130</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+    <row r="8" spans="1:11" ht="15" thickBot="1">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>5</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>34</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <v>180</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+    <row r="9" spans="1:11" ht="15" thickBot="1">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>2.5</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>20</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <v>120</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+    <row r="10" spans="1:11" ht="15" thickBot="1">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>1.5</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>12</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <v>170</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+    <row r="11" spans="1:11" ht="15" thickBot="1">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>3.5</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>11</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>200</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+    <row r="12" spans="1:11" ht="15" thickBot="1">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>1.2</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <v>15</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <v>250</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+    <row r="13" spans="1:11" ht="15" thickBot="1">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>3</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <v>18</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <v>200</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="K13" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+    <row r="14" spans="1:11" ht="15" thickBot="1">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <v>16</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <v>140</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+    <row r="15" spans="1:11" ht="15" thickBot="1">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>1.8</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <v>14</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <v>190</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="2" t="s">
         <v>78</v>
       </c>
     </row>
